--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="501">
   <si>
     <t>Filename</t>
   </si>
@@ -808,703 +808,715 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9644,0.0096,0.0013,0.0040</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9906,0.0005,0.0004,0.0030</t>
-  </si>
-  <si>
-    <t>0.0020,0.0105,0.0005,0.9981</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9855,0.0033,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9953,0.0001,0.0000,0.0028</t>
+  </si>
+  <si>
+    <t>0.0014,0.0056,0.0020,0.9979</t>
+  </si>
+  <si>
+    <t>0.9968,0.0014,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0019,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0014,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9479,0.0004,0.0514,0.0005</t>
+  </si>
+  <si>
+    <t>0.0028,0.0004,0.9953,0.0002</t>
+  </si>
+  <si>
+    <t>0.0289,0.0021,0.9682,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.0005,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.9831,0.0001,0.0264,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9971,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9986,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0784,0.0007,0.9234,0.0005</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.2128,0.0002,0.8951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0000,0.9956,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.7984,0.3330,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9655,0.0134,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.0010,0.9999,0.0253</t>
+  </si>
+  <si>
+    <t>0.0006,0.9928,0.0261,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0013,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.0027,0.9918,0.0021</t>
+  </si>
+  <si>
+    <t>0.4669,0.5597,0.0070,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.9946,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.0032,0.9824,0.0016</t>
+  </si>
+  <si>
+    <t>0.0017,0.0143,0.9919,0.0023</t>
+  </si>
+  <si>
+    <t>0.0234,0.0193,0.9335,0.0006</t>
+  </si>
+  <si>
+    <t>0.0129,0.0000,0.9863,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0013,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9873,0.0003,0.1448</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0065,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.9965,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9979,0.0005</t>
+  </si>
+  <si>
+    <t>0.9987,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0029,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0044</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0007,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9913,0.0072,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.7843,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0069,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.9964,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9946,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9984,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0002,0.0065,0.0001</t>
+  </si>
+  <si>
+    <t>0.8541,0.0038,0.1014,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.0033,0.9975,0.0054</t>
+  </si>
+  <si>
+    <t>0.0000,0.9795,0.9909,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.2649,0.9624,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.0266,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.0151,0.9973</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0020,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9978,0.3805,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9600,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9669,0.6406,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.3538,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9843,0.8700,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9979,0.0701,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0016,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0015,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9943,0.0058,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0014,0.9967,0.0005</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.9947,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0044,0.9889,0.0024,0.0019</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8235,0.1889,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.8646,0.0010,0.0759,0.0039</t>
+  </si>
+  <si>
+    <t>0.9266,0.0003,0.0955,0.0001</t>
+  </si>
+  <si>
+    <t>0.2487,0.0302,0.2890,0.0152</t>
+  </si>
+  <si>
+    <t>0.8574,0.0002,0.1932,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0019,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9965,0.8570,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9989,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9351,0.0723,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9549,0.0351,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0009,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0001,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9986,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9935,0.0001,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.0108,0.0007,0.9866,0.0002</t>
-  </si>
-  <si>
-    <t>0.4890,0.0014,0.5779,0.0000</t>
-  </si>
-  <si>
-    <t>0.1130,0.0002,0.9254,0.0001</t>
-  </si>
-  <si>
-    <t>0.9832,0.0001,0.0245,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9971,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.2355,0.0015,0.7724,0.0006</t>
-  </si>
-  <si>
-    <t>0.9755,0.0002,0.0238,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0532,0.0001,0.9659,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9991,0.0005</t>
-  </si>
-  <si>
-    <t>0.0149,0.9858,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9973,0.0017,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0496</t>
-  </si>
-  <si>
-    <t>0.0060,0.9695,0.0182,0.0000</t>
-  </si>
-  <si>
-    <t>0.9852,0.0071,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.1928,0.0046,0.6966,0.0026</t>
-  </si>
-  <si>
-    <t>0.0491,0.9523,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.9909,0.0765,0.0002</t>
-  </si>
-  <si>
-    <t>0.0048,0.0042,0.9751,0.0019</t>
-  </si>
-  <si>
-    <t>0.0001,0.0019,0.9990,0.0034</t>
-  </si>
-  <si>
-    <t>0.0236,0.0059,0.9574,0.0005</t>
-  </si>
-  <si>
-    <t>0.0097,0.0000,0.9877,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0175,0.9950,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9982,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9943,0.0002,0.3684</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9995,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0108,0.0000,0.9902,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0000,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9991,0.0003</t>
-  </si>
-  <si>
-    <t>0.9882,0.0142,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9896,0.0135,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0040</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8707,0.9580,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0224,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9987,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9874,0.0005,0.0102,0.0001</t>
-  </si>
-  <si>
-    <t>0.9077,0.0147,0.0228,0.0033</t>
-  </si>
-  <si>
-    <t>0.0017,0.0013,0.9963,0.0123</t>
-  </si>
-  <si>
-    <t>0.0000,0.9652,0.9925,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9913,0.9729,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9869,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.0005,0.9994</t>
+    <t>0.9983,0.0007,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7138,0.9861,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.0740,0.9688,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9940,0.0018,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0074,0.0000,0.9923,0.0001</t>
+  </si>
+  <si>
+    <t>0.8289,0.0017,0.1783,0.0006</t>
+  </si>
+  <si>
+    <t>0.0493,0.0004,0.0001,0.9800</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0004,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0057,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9712,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9951,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9616,0.5931,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.8396,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.9776,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9876,0.9231,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0008,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0048,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0046,0.0001,0.0001</t>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9937,0.7369,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.9900,0.0016,0.0078</t>
+  </si>
+  <si>
+    <t>0.4926,0.4302,0.0091,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2659,0.0000,0.0003,0.8971</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0040,0.9988,0.0147</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9095,0.0021,0.0253,0.0063</t>
+  </si>
+  <si>
+    <t>0.0424,0.9387,0.0044,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0023,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7701,0.0837,0.0232,0.0009</t>
+  </si>
+  <si>
+    <t>0.9853,0.0045,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.9945,0.0020,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0011,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0018,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9363,0.0298,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.1404,0.9002,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.6962,0.4624,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9323,0.0007,0.0835,0.0003</t>
+  </si>
+  <si>
+    <t>0.8897,0.0917,0.0058,0.0009</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0027,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.6026,0.3729,0.0027,0.0020</t>
+  </si>
+  <si>
+    <t>0.0000,0.0052,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0218,0.9948,0.0003</t>
+  </si>
+  <si>
+    <t>0.0034,0.0000,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0488,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9992,0.0007</t>
+  </si>
+  <si>
+    <t>0.0307,0.0052,0.9555,0.0003</t>
+  </si>
+  <si>
+    <t>0.0116,0.0018,0.9880,0.0003</t>
+  </si>
+  <si>
+    <t>0.0550,0.0020,0.9315,0.0013</t>
+  </si>
+  <si>
+    <t>0.0254,0.0080,0.9438,0.0015</t>
+  </si>
+  <si>
+    <t>0.0025,0.0051,0.9924,0.0006</t>
+  </si>
+  <si>
+    <t>0.9903,0.0002,0.0080,0.0000</t>
+  </si>
+  <si>
+    <t>0.8187,0.0030,0.1014,0.0078</t>
+  </si>
+  <si>
+    <t>0.3774,0.0003,0.6434,0.0009</t>
+  </si>
+  <si>
+    <t>0.0022,0.9971,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.9965,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.1398,0.8839,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0053,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4390,0.6642,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.5909,0.2272,0.0091,0.0021</t>
+  </si>
+  <si>
+    <t>0.9965,0.0000,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.9599,0.0029,0.0089,0.0055</t>
+  </si>
+  <si>
+    <t>0.8967,0.0093,0.0668,0.0020</t>
+  </si>
+  <si>
+    <t>0.9951,0.0000,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9996,0.0014</t>
+  </si>
+  <si>
+    <t>0.0391,0.0055,0.9255,0.0022</t>
+  </si>
+  <si>
+    <t>0.0022,0.0038,0.9939,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0167,0.0068,0.9609,0.0005</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9862,0.0124,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9900,0.0083,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0032,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0039,0.9982,0.0006</t>
+  </si>
+  <si>
+    <t>0.4686,0.0959,0.2012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9323,0.0003,0.0231,0.0095</t>
+  </si>
+  <si>
+    <t>0.0024,0.0001,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.7564,0.9578,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.0020,0.9953,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0061,0.0015,0.9887,0.0004</t>
+  </si>
+  <si>
+    <t>0.9922,0.0001,0.0059,0.0001</t>
+  </si>
+  <si>
+    <t>0.9726,0.0004,0.0282,0.0001</t>
+  </si>
+  <si>
+    <t>0.9869,0.0009,0.0045,0.0001</t>
   </si>
   <si>
     <t>0.9990,0.0006,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9977,0.0020,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0016,0.0000,0.0000</t>
+    <t>0.9991,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9876,0.0155,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0040,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0010,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9992,0.0003,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0008,0.9966,0.0005</t>
-  </si>
-  <si>
-    <t>0.0178,0.0007,0.9824,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.9957,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.0047,0.9918,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8576,0.1655,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0277,0.0091,0.9137,0.0056</t>
-  </si>
-  <si>
-    <t>0.9915,0.0001,0.0068,0.0000</t>
-  </si>
-  <si>
-    <t>0.9787,0.0040,0.0036,0.0005</t>
-  </si>
-  <si>
-    <t>0.9713,0.0014,0.0119,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0152,0.0000,0.9980</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9877,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9982,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.8340,0.1143,0.0094,0.0003</t>
-  </si>
-  <si>
-    <t>0.9370,0.0622,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9099,0.7097,0.0010</t>
-  </si>
-  <si>
-    <t>0.0012,0.2397,0.9620,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0017,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0954,0.0024,0.8809,0.0077</t>
-  </si>
-  <si>
-    <t>0.0173,0.0002,0.9817,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0001,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.1521,0.0000,0.0001,0.9647</t>
-  </si>
-  <si>
-    <t>0.0000,0.9960,0.6738,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.9947,0.0010,0.0027</t>
-  </si>
-  <si>
-    <t>0.0436,0.9502,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.6464,0.0000,0.0010,0.4231</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0108,0.9984,0.0062</t>
-  </si>
-  <si>
-    <t>0.9926,0.0001,0.0036,0.0017</t>
-  </si>
-  <si>
-    <t>0.9692,0.0002,0.0181,0.0010</t>
-  </si>
-  <si>
-    <t>0.1993,0.8200,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8607,0.0142,0.0400,0.0006</t>
-  </si>
-  <si>
-    <t>0.9616,0.0102,0.0107,0.0002</t>
-  </si>
-  <si>
-    <t>0.9541,0.0368,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9974,0.0004,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0025,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9354,0.0280,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.6799,0.3665,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.3378,0.7637,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0011,0.9946,0.0007</t>
-  </si>
-  <si>
-    <t>0.9936,0.0043,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9943,0.0041,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9313,0.0651,0.0048,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0038,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9955,0.0014,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0103,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0233,0.0000,0.9759,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0098,0.9992,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0142,0.0002,0.9870,0.0001</t>
-  </si>
-  <si>
-    <t>0.0094,0.0003,0.9908,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.0005,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.0396,0.0151,0.9136,0.0007</t>
-  </si>
-  <si>
-    <t>0.0125,0.5740,0.3403,0.0006</t>
-  </si>
-  <si>
-    <t>0.0875,0.0027,0.9202,0.0006</t>
-  </si>
-  <si>
-    <t>0.3629,0.0063,0.4093,0.0022</t>
-  </si>
-  <si>
-    <t>0.4021,0.0013,0.6044,0.0012</t>
-  </si>
-  <si>
-    <t>0.0108,0.9923,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5789,0.4597,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.6972,0.2866,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.9596,0.0708,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5843,0.1334,0.0791,0.0019</t>
-  </si>
-  <si>
-    <t>0.9980,0.0000,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9693,0.0023,0.0006,0.0041</t>
-  </si>
-  <si>
-    <t>0.0318,0.0015,0.9679,0.0006</t>
-  </si>
-  <si>
-    <t>0.9562,0.0003,0.0367,0.0014</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9991,0.0006</t>
-  </si>
-  <si>
-    <t>0.0080,0.1292,0.9011,0.0120</t>
-  </si>
-  <si>
-    <t>0.0013,0.0799,0.9941,0.0002</t>
-  </si>
-  <si>
-    <t>0.0060,0.0024,0.9893,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0011,0.9975,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0013,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9524,0.0240,0.0040,0.0082</t>
-  </si>
-  <si>
-    <t>0.9986,0.0011,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0032,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9994,0.0010</t>
-  </si>
-  <si>
-    <t>0.1469,0.1902,0.2690,0.0031</t>
-  </si>
-  <si>
-    <t>0.8555,0.0019,0.0425,0.0293</t>
-  </si>
-  <si>
-    <t>0.0065,0.0003,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.2972,0.8957,0.0012</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.9971,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0046,0.0203,0.9808,0.0028</t>
-  </si>
-  <si>
-    <t>0.9967,0.0000,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.7610,0.0030,0.2849,0.0004</t>
-  </si>
-  <si>
-    <t>0.9946,0.0001,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0015,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9911,0.0103,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9883,0.0132,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0023,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9911,0.0097,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9940,0.0033,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.0013,0.0694,0.9861,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0045,0.9928,0.0025</t>
-  </si>
-  <si>
-    <t>0.0050,0.0066,0.9795,0.0021</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0001,0.9944,0.0030</t>
-  </si>
-  <si>
-    <t>0.0072,0.0006,0.9842,0.0021</t>
-  </si>
-  <si>
-    <t>0.0004,0.0009,0.9976,0.0019</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.0034,0.0011,0.0000,0.9988</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.0008,0.9989</t>
-  </si>
-  <si>
-    <t>0.9309,0.0001,0.0000,0.0863</t>
+    <t>0.0023,0.0120,0.9908,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0044,0.9973,0.0010</t>
+  </si>
+  <si>
+    <t>0.0079,0.0306,0.9431,0.0017</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0094,0.0002,0.9801,0.0069</t>
+  </si>
+  <si>
+    <t>0.0038,0.0001,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9971,0.0027</t>
+  </si>
+  <si>
+    <t>0.9120,0.0001,0.0152,0.0336</t>
+  </si>
+  <si>
+    <t>0.0109,0.0007,0.0000,0.9970</t>
+  </si>
+  <si>
+    <t>0.0110,0.0002,0.0014,0.9925</t>
+  </si>
+  <si>
+    <t>0.9176,0.0003,0.0003,0.0808</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1902,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1904,7 +1916,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1918,7 +1930,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1932,7 +1944,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1946,7 +1958,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1960,7 +1972,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1974,7 +1986,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1988,7 +2000,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2002,7 +2014,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2016,7 +2028,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2030,7 +2042,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2044,7 +2056,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2058,7 +2070,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2072,7 +2084,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2086,7 +2098,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2100,7 +2112,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2114,7 +2126,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2128,7 +2140,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2142,7 +2154,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2156,7 +2168,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2170,7 +2182,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2184,7 +2196,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2198,7 +2210,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2212,7 +2224,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2226,7 +2238,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2240,7 +2252,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2254,7 +2266,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2268,7 +2280,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2282,7 +2294,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2293,10 +2305,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2310,7 +2322,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2324,7 +2336,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2338,7 +2350,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2352,7 +2364,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2366,7 +2378,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2380,7 +2392,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2394,7 +2406,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2408,7 +2420,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2422,7 +2434,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2436,7 +2448,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2450,7 +2462,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2464,7 +2476,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2478,7 +2490,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2492,7 +2504,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2506,7 +2518,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2520,7 +2532,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2534,7 +2546,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2548,7 +2560,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2702,7 +2714,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2716,7 +2728,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2730,7 +2742,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2744,7 +2756,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2758,7 +2770,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2772,7 +2784,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2786,7 +2798,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2800,7 +2812,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2814,7 +2826,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2828,7 +2840,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2842,7 +2854,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2856,7 +2868,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2870,7 +2882,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2884,7 +2896,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2895,10 +2907,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2912,7 +2924,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2923,10 +2935,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2940,7 +2952,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2954,7 +2966,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2968,7 +2980,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2982,7 +2994,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2996,7 +3008,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3010,7 +3022,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3021,10 +3033,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3038,7 +3050,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3052,7 +3064,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3063,10 +3075,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3080,7 +3092,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3091,10 +3103,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3108,7 +3120,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3122,7 +3134,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3136,7 +3148,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3150,7 +3162,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3164,7 +3176,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3178,7 +3190,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3192,7 +3204,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3206,7 +3218,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>271</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3220,7 +3232,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3234,7 +3246,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3248,7 +3260,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3262,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>357</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3276,7 +3288,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3290,7 +3302,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3304,7 +3316,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3318,7 +3330,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3332,7 +3344,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3346,7 +3358,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3360,7 +3372,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3374,7 +3386,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3388,7 +3400,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3402,7 +3414,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>364</v>
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3416,7 +3428,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3430,7 +3442,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3444,7 +3456,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3458,7 +3470,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3472,7 +3484,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3483,10 +3495,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,7 +3512,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3511,10 +3523,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3528,7 +3540,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3542,7 +3554,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3556,7 +3568,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3570,7 +3582,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>375</v>
+        <v>330</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3584,7 +3596,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3598,7 +3610,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3612,7 +3624,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3626,7 +3638,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3640,7 +3652,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3654,7 +3666,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3668,7 +3680,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3682,7 +3694,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3696,7 +3708,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3710,7 +3722,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3724,7 +3736,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3738,7 +3750,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3752,7 +3764,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3766,7 +3778,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3780,7 +3792,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3794,7 +3806,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3808,7 +3820,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3822,7 +3834,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>271</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3833,10 +3845,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3850,7 +3862,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3864,7 +3876,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3878,7 +3890,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3892,7 +3904,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3906,7 +3918,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>338</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3920,7 +3932,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>338</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3934,7 +3946,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3948,7 +3960,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3962,7 +3974,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3976,7 +3988,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>356</v>
+        <v>401</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3987,10 +3999,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4004,7 +4016,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4015,10 +4027,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4032,7 +4044,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4046,7 +4058,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4060,7 +4072,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4074,7 +4086,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4088,7 +4100,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4102,7 +4114,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4116,7 +4128,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4130,7 +4142,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4144,7 +4156,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4158,7 +4170,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4172,7 +4184,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4186,7 +4198,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4200,7 +4212,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4214,7 +4226,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4228,7 +4240,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4242,7 +4254,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4256,7 +4268,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4270,7 +4282,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4284,7 +4296,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4295,10 +4307,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4309,10 +4321,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4323,10 +4335,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4340,7 +4352,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4354,7 +4366,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4368,7 +4380,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4382,7 +4394,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4396,7 +4408,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4410,7 +4422,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4424,7 +4436,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4438,7 +4450,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4452,7 +4464,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4466,7 +4478,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4480,7 +4492,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4494,7 +4506,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4508,7 +4520,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4522,7 +4534,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4536,7 +4548,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4550,7 +4562,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4564,7 +4576,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4575,10 +4587,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4589,10 +4601,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4606,7 +4618,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4620,7 +4632,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4634,7 +4646,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4648,7 +4660,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4659,10 +4671,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4676,7 +4688,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4687,10 +4699,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4704,7 +4716,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4718,7 +4730,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4732,7 +4744,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4743,10 +4755,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4760,7 +4772,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4774,7 +4786,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4788,7 +4800,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4802,7 +4814,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4816,7 +4828,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4830,7 +4842,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4844,7 +4856,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4858,7 +4870,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4872,7 +4884,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4886,7 +4898,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4900,7 +4912,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4914,7 +4926,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>412</v>
+        <v>468</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4928,7 +4940,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>463</v>
+        <v>382</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4942,7 +4954,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4956,7 +4968,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4967,10 +4979,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4984,7 +4996,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4998,7 +5010,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5012,7 +5024,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5023,10 +5035,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5040,7 +5052,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5054,7 +5066,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5068,7 +5080,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>327</v>
+        <v>477</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5082,7 +5094,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5096,7 +5108,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5110,7 +5122,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5124,7 +5136,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5138,7 +5150,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5152,7 +5164,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5166,7 +5178,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5180,7 +5192,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5194,7 +5206,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5208,7 +5220,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>481</v>
+        <v>386</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5222,7 +5234,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5236,7 +5248,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5250,7 +5262,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5264,7 +5276,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5278,7 +5290,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5292,7 +5304,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5306,7 +5318,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5320,7 +5332,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5334,7 +5346,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5348,7 +5360,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5362,7 +5374,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5376,7 +5388,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5390,7 +5402,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5404,7 +5416,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5418,7 +5430,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5432,7 +5444,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5446,7 +5458,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
